--- a/PhysicalsActual.xlsx
+++ b/PhysicalsActual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ken/PycharmProjects/emissionsGreenHouseGas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A97F39-315D-2E4C-B5A1-9658BE2F20F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34424E47-5F87-5B43-B817-1B699DE38A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,19 +118,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -147,7 +141,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -155,149 +149,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -308,38 +171,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A452F7F7-D3CC-E84E-9480-2EFAF2280309}" name="Table13" displayName="Table13" ref="A1:D119" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:D119" xr:uid="{A452F7F7-D3CC-E84E-9480-2EFAF2280309}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D119">
-    <sortCondition ref="C1:C119"/>
-  </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E5C166E0-6F64-3E49-8296-9768F3EA9891}" name="Date" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{CA843D2C-349A-CF47-8B88-25B5E9F76FEF}" name="Group"/>
-    <tableColumn id="3" xr3:uid="{2FE2B17F-A7D2-3E41-9C24-D5CED054E51A}" name="Metric"/>
-    <tableColumn id="4" xr3:uid="{C05B0766-5A72-5143-9D85-6D910275C222}" name="Value"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D94ED07E-E846-994B-85AC-3B6C2EE1A437}" name="Table1" displayName="Table1" ref="A1:D119" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
-  <autoFilter ref="A1:D119" xr:uid="{D94ED07E-E846-994B-85AC-3B6C2EE1A437}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D119">
-    <sortCondition ref="C1:C119"/>
-  </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D41E1B12-3B8F-374A-93FC-168C5CB47A3A}" name="Date" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{B12A8D97-367A-B447-A590-A3D3265F19DA}" name="Group"/>
-    <tableColumn id="3" xr3:uid="{2CD32345-A25C-C148-B92B-66A2321BDA73}" name="Metric"/>
-    <tableColumn id="4" xr3:uid="{291F4387-83AA-FA4B-B022-23EB7B1668C2}" name="Value"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,26 +461,26 @@
   <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>44197</v>
       </c>
       <c r="B2" t="s">
@@ -663,7 +494,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>44228</v>
       </c>
       <c r="B3" t="s">
@@ -677,7 +508,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>44256</v>
       </c>
       <c r="B4" t="s">
@@ -691,7 +522,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>44287</v>
       </c>
       <c r="B5" t="s">
@@ -705,7 +536,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>44317</v>
       </c>
       <c r="B6" t="s">
@@ -719,7 +550,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>44348</v>
       </c>
       <c r="B7" t="s">
@@ -733,7 +564,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>44378</v>
       </c>
       <c r="B8" t="s">
@@ -747,7 +578,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>44409</v>
       </c>
       <c r="B9" t="s">
@@ -761,7 +592,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>44440</v>
       </c>
       <c r="B10" t="s">
@@ -775,7 +606,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>44470</v>
       </c>
       <c r="B11" t="s">
@@ -789,7 +620,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>44501</v>
       </c>
       <c r="B12" t="s">
@@ -803,7 +634,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>44531</v>
       </c>
       <c r="B13" t="s">
@@ -817,7 +648,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>44197</v>
       </c>
       <c r="B14" t="s">
@@ -831,7 +662,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>44228</v>
       </c>
       <c r="B15" t="s">
@@ -845,7 +676,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>44256</v>
       </c>
       <c r="B16" t="s">
@@ -859,7 +690,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>44287</v>
       </c>
       <c r="B17" t="s">
@@ -873,7 +704,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>44317</v>
       </c>
       <c r="B18" t="s">
@@ -887,7 +718,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>44348</v>
       </c>
       <c r="B19" t="s">
@@ -901,7 +732,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>44378</v>
       </c>
       <c r="B20" t="s">
@@ -915,7 +746,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>44409</v>
       </c>
       <c r="B21" t="s">
@@ -929,7 +760,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>44440</v>
       </c>
       <c r="B22" t="s">
@@ -943,7 +774,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>44470</v>
       </c>
       <c r="B23" t="s">
@@ -957,7 +788,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>44501</v>
       </c>
       <c r="B24" t="s">
@@ -971,7 +802,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>44531</v>
       </c>
       <c r="B25" t="s">
@@ -985,7 +816,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>44197</v>
       </c>
       <c r="B26" t="s">
@@ -999,7 +830,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>44228</v>
       </c>
       <c r="B27" t="s">
@@ -1013,7 +844,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>44256</v>
       </c>
       <c r="B28" t="s">
@@ -1027,7 +858,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>44287</v>
       </c>
       <c r="B29" t="s">
@@ -1041,7 +872,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>44317</v>
       </c>
       <c r="B30" t="s">
@@ -1055,7 +886,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>44348</v>
       </c>
       <c r="B31" t="s">
@@ -1069,7 +900,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>44378</v>
       </c>
       <c r="B32" t="s">
@@ -1083,7 +914,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>44409</v>
       </c>
       <c r="B33" t="s">
@@ -1097,7 +928,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>44440</v>
       </c>
       <c r="B34" t="s">
@@ -1111,7 +942,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>44470</v>
       </c>
       <c r="B35" t="s">
@@ -1125,7 +956,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>44501</v>
       </c>
       <c r="B36" t="s">
@@ -1139,7 +970,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>44531</v>
       </c>
       <c r="B37" t="s">
@@ -1153,7 +984,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>44197</v>
       </c>
       <c r="B38" t="s">
@@ -1167,7 +998,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>44228</v>
       </c>
       <c r="B39" t="s">
@@ -1181,7 +1012,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>44256</v>
       </c>
       <c r="B40" t="s">
@@ -1195,7 +1026,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>44287</v>
       </c>
       <c r="B41" t="s">
@@ -1209,7 +1040,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>44317</v>
       </c>
       <c r="B42" t="s">
@@ -1223,7 +1054,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>44348</v>
       </c>
       <c r="B43" t="s">
@@ -1237,7 +1068,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>44378</v>
       </c>
       <c r="B44" t="s">
@@ -1251,7 +1082,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>44409</v>
       </c>
       <c r="B45" t="s">
@@ -1265,7 +1096,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>44440</v>
       </c>
       <c r="B46" t="s">
@@ -1279,7 +1110,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>44470</v>
       </c>
       <c r="B47" t="s">
@@ -1293,7 +1124,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>44501</v>
       </c>
       <c r="B48" t="s">
@@ -1307,7 +1138,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>44531</v>
       </c>
       <c r="B49" t="s">
@@ -1321,7 +1152,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>44197</v>
       </c>
       <c r="B50" t="s">
@@ -1335,7 +1166,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>44228</v>
       </c>
       <c r="B51" t="s">
@@ -1349,7 +1180,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>44256</v>
       </c>
       <c r="B52" t="s">
@@ -1363,7 +1194,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>44287</v>
       </c>
       <c r="B53" t="s">
@@ -1377,7 +1208,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
+      <c r="A54" s="1">
         <v>44317</v>
       </c>
       <c r="B54" t="s">
@@ -1391,7 +1222,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
+      <c r="A55" s="1">
         <v>44348</v>
       </c>
       <c r="B55" t="s">
@@ -1405,7 +1236,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
+      <c r="A56" s="1">
         <v>44378</v>
       </c>
       <c r="B56" t="s">
@@ -1419,7 +1250,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
+      <c r="A57" s="1">
         <v>44409</v>
       </c>
       <c r="B57" t="s">
@@ -1433,7 +1264,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
+      <c r="A58" s="1">
         <v>44440</v>
       </c>
       <c r="B58" t="s">
@@ -1447,7 +1278,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
+      <c r="A59" s="1">
         <v>44470</v>
       </c>
       <c r="B59" t="s">
@@ -1461,7 +1292,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
+      <c r="A60" s="1">
         <v>44501</v>
       </c>
       <c r="B60" t="s">
@@ -1475,7 +1306,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
+      <c r="A61" s="1">
         <v>44531</v>
       </c>
       <c r="B61" t="s">
@@ -1489,7 +1320,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
+      <c r="A62" s="1">
         <v>44197</v>
       </c>
       <c r="B62" t="s">
@@ -1503,7 +1334,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
+      <c r="A63" s="1">
         <v>44228</v>
       </c>
       <c r="B63" t="s">
@@ -1517,7 +1348,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
+      <c r="A64" s="1">
         <v>44256</v>
       </c>
       <c r="B64" t="s">
@@ -1531,7 +1362,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
+      <c r="A65" s="1">
         <v>44287</v>
       </c>
       <c r="B65" t="s">
@@ -1545,7 +1376,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
+      <c r="A66" s="1">
         <v>44317</v>
       </c>
       <c r="B66" t="s">
@@ -1559,7 +1390,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
+      <c r="A67" s="1">
         <v>44348</v>
       </c>
       <c r="B67" t="s">
@@ -1573,7 +1404,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
+      <c r="A68" s="1">
         <v>44378</v>
       </c>
       <c r="B68" t="s">
@@ -1587,7 +1418,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
+      <c r="A69" s="1">
         <v>44409</v>
       </c>
       <c r="B69" t="s">
@@ -1601,7 +1432,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
+      <c r="A70" s="1">
         <v>44440</v>
       </c>
       <c r="B70" t="s">
@@ -1615,7 +1446,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>44470</v>
       </c>
       <c r="B71" t="s">
@@ -1629,7 +1460,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
+      <c r="A72" s="1">
         <v>44501</v>
       </c>
       <c r="B72" t="s">
@@ -1643,7 +1474,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="A73" s="1">
         <v>44531</v>
       </c>
       <c r="B73" t="s">
@@ -1657,7 +1488,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="A74" s="1">
         <v>44197</v>
       </c>
       <c r="B74" t="s">
@@ -1671,7 +1502,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="A75" s="1">
         <v>44228</v>
       </c>
       <c r="B75" t="s">
@@ -1685,7 +1516,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="A76" s="1">
         <v>44256</v>
       </c>
       <c r="B76" t="s">
@@ -1699,7 +1530,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
+      <c r="A77" s="1">
         <v>44287</v>
       </c>
       <c r="B77" t="s">
@@ -1713,7 +1544,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="A78" s="1">
         <v>44317</v>
       </c>
       <c r="B78" t="s">
@@ -1727,7 +1558,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="A79" s="1">
         <v>44348</v>
       </c>
       <c r="B79" t="s">
@@ -1741,7 +1572,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
+      <c r="A80" s="1">
         <v>44378</v>
       </c>
       <c r="B80" t="s">
@@ -1755,7 +1586,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
+      <c r="A81" s="1">
         <v>44440</v>
       </c>
       <c r="B81" t="s">
@@ -1769,7 +1600,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="A82" s="1">
         <v>44470</v>
       </c>
       <c r="B82" t="s">
@@ -1783,7 +1614,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
+      <c r="A83" s="1">
         <v>44501</v>
       </c>
       <c r="B83" t="s">
@@ -1797,7 +1628,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
+      <c r="A84" s="1">
         <v>44197</v>
       </c>
       <c r="B84" t="s">
@@ -1811,7 +1642,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
+      <c r="A85" s="1">
         <v>44228</v>
       </c>
       <c r="B85" t="s">
@@ -1825,7 +1656,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
+      <c r="A86" s="1">
         <v>44256</v>
       </c>
       <c r="B86" t="s">
@@ -1839,7 +1670,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="A87" s="1">
         <v>44287</v>
       </c>
       <c r="B87" t="s">
@@ -1853,7 +1684,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
+      <c r="A88" s="1">
         <v>44317</v>
       </c>
       <c r="B88" t="s">
@@ -1867,7 +1698,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="A89" s="1">
         <v>44348</v>
       </c>
       <c r="B89" t="s">
@@ -1881,7 +1712,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
+      <c r="A90" s="1">
         <v>44378</v>
       </c>
       <c r="B90" t="s">
@@ -1895,7 +1726,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="A91" s="1">
         <v>44409</v>
       </c>
       <c r="B91" t="s">
@@ -1909,7 +1740,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
+      <c r="A92" s="1">
         <v>44440</v>
       </c>
       <c r="B92" t="s">
@@ -1923,7 +1754,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
+      <c r="A93" s="1">
         <v>44470</v>
       </c>
       <c r="B93" t="s">
@@ -1937,7 +1768,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
+      <c r="A94" s="1">
         <v>44501</v>
       </c>
       <c r="B94" t="s">
@@ -1951,7 +1782,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
+      <c r="A95" s="1">
         <v>44531</v>
       </c>
       <c r="B95" t="s">
@@ -1965,7 +1796,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
+      <c r="A96" s="1">
         <v>44197</v>
       </c>
       <c r="B96" t="s">
@@ -1979,7 +1810,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
+      <c r="A97" s="1">
         <v>44228</v>
       </c>
       <c r="B97" t="s">
@@ -1993,7 +1824,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
+      <c r="A98" s="1">
         <v>44256</v>
       </c>
       <c r="B98" t="s">
@@ -2007,7 +1838,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
+      <c r="A99" s="1">
         <v>44287</v>
       </c>
       <c r="B99" t="s">
@@ -2021,7 +1852,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
+      <c r="A100" s="1">
         <v>44317</v>
       </c>
       <c r="B100" t="s">
@@ -2035,7 +1866,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="3">
+      <c r="A101" s="1">
         <v>44348</v>
       </c>
       <c r="B101" t="s">
@@ -2049,7 +1880,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="3">
+      <c r="A102" s="1">
         <v>44378</v>
       </c>
       <c r="B102" t="s">
@@ -2063,7 +1894,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
+      <c r="A103" s="1">
         <v>44409</v>
       </c>
       <c r="B103" t="s">
@@ -2077,7 +1908,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="3">
+      <c r="A104" s="1">
         <v>44440</v>
       </c>
       <c r="B104" t="s">
@@ -2091,7 +1922,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="3">
+      <c r="A105" s="1">
         <v>44470</v>
       </c>
       <c r="B105" t="s">
@@ -2105,7 +1936,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
+      <c r="A106" s="1">
         <v>44501</v>
       </c>
       <c r="B106" t="s">
@@ -2119,7 +1950,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
+      <c r="A107" s="1">
         <v>44531</v>
       </c>
       <c r="B107" t="s">
@@ -2133,7 +1964,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
+      <c r="A108" s="1">
         <v>44197</v>
       </c>
       <c r="B108" t="s">
@@ -2147,7 +1978,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
+      <c r="A109" s="1">
         <v>44228</v>
       </c>
       <c r="B109" t="s">
@@ -2161,7 +1992,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
+      <c r="A110" s="1">
         <v>44256</v>
       </c>
       <c r="B110" t="s">
@@ -2175,7 +2006,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
+      <c r="A111" s="1">
         <v>44287</v>
       </c>
       <c r="B111" t="s">
@@ -2189,7 +2020,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
+      <c r="A112" s="1">
         <v>44317</v>
       </c>
       <c r="B112" t="s">
@@ -2203,7 +2034,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
+      <c r="A113" s="1">
         <v>44348</v>
       </c>
       <c r="B113" t="s">
@@ -2217,7 +2048,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
+      <c r="A114" s="1">
         <v>44378</v>
       </c>
       <c r="B114" t="s">
@@ -2231,7 +2062,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
+      <c r="A115" s="1">
         <v>44409</v>
       </c>
       <c r="B115" t="s">
@@ -2245,7 +2076,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
+      <c r="A116" s="1">
         <v>44440</v>
       </c>
       <c r="B116" t="s">
@@ -2259,7 +2090,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
+      <c r="A117" s="1">
         <v>44470</v>
       </c>
       <c r="B117" t="s">
@@ -2273,7 +2104,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
+      <c r="A118" s="1">
         <v>44501</v>
       </c>
       <c r="B118" t="s">
@@ -2287,7 +2118,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
+      <c r="A119" s="1">
         <v>44531</v>
       </c>
       <c r="B119" t="s">
@@ -2302,9 +2133,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2313,26 +2141,26 @@
   <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>44562</v>
       </c>
       <c r="B2" t="s">
@@ -2346,7 +2174,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>44593</v>
       </c>
       <c r="B3" t="s">
@@ -2360,7 +2188,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>44621</v>
       </c>
       <c r="B4" t="s">
@@ -2374,7 +2202,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>44652</v>
       </c>
       <c r="B5" t="s">
@@ -2388,7 +2216,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>44682</v>
       </c>
       <c r="B6" t="s">
@@ -2402,7 +2230,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>44713</v>
       </c>
       <c r="B7" t="s">
@@ -2416,7 +2244,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>44743</v>
       </c>
       <c r="B8" t="s">
@@ -2430,7 +2258,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>44774</v>
       </c>
       <c r="B9" t="s">
@@ -2444,7 +2272,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>44805</v>
       </c>
       <c r="B10" t="s">
@@ -2458,7 +2286,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>44835</v>
       </c>
       <c r="B11" t="s">
@@ -2472,7 +2300,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>44866</v>
       </c>
       <c r="B12" t="s">
@@ -2486,7 +2314,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>44896</v>
       </c>
       <c r="B13" t="s">
@@ -2500,7 +2328,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>44562</v>
       </c>
       <c r="B14" t="s">
@@ -2514,7 +2342,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>44593</v>
       </c>
       <c r="B15" t="s">
@@ -2528,7 +2356,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>44621</v>
       </c>
       <c r="B16" t="s">
@@ -2542,7 +2370,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>44652</v>
       </c>
       <c r="B17" t="s">
@@ -2556,7 +2384,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>44682</v>
       </c>
       <c r="B18" t="s">
@@ -2570,7 +2398,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>44713</v>
       </c>
       <c r="B19" t="s">
@@ -2584,7 +2412,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>44743</v>
       </c>
       <c r="B20" t="s">
@@ -2598,7 +2426,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>44774</v>
       </c>
       <c r="B21" t="s">
@@ -2612,7 +2440,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>44805</v>
       </c>
       <c r="B22" t="s">
@@ -2626,7 +2454,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>44835</v>
       </c>
       <c r="B23" t="s">
@@ -2640,7 +2468,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>44866</v>
       </c>
       <c r="B24" t="s">
@@ -2654,7 +2482,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>44896</v>
       </c>
       <c r="B25" t="s">
@@ -2668,7 +2496,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>44562</v>
       </c>
       <c r="B26" t="s">
@@ -2682,7 +2510,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>44593</v>
       </c>
       <c r="B27" t="s">
@@ -2696,7 +2524,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>44621</v>
       </c>
       <c r="B28" t="s">
@@ -2710,7 +2538,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>44652</v>
       </c>
       <c r="B29" t="s">
@@ -2724,7 +2552,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>44682</v>
       </c>
       <c r="B30" t="s">
@@ -2738,7 +2566,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>44713</v>
       </c>
       <c r="B31" t="s">
@@ -2752,7 +2580,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>44743</v>
       </c>
       <c r="B32" t="s">
@@ -2766,7 +2594,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>44774</v>
       </c>
       <c r="B33" t="s">
@@ -2780,7 +2608,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>44805</v>
       </c>
       <c r="B34" t="s">
@@ -2794,7 +2622,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>44835</v>
       </c>
       <c r="B35" t="s">
@@ -2808,7 +2636,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>44866</v>
       </c>
       <c r="B36" t="s">
@@ -2822,7 +2650,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>44896</v>
       </c>
       <c r="B37" t="s">
@@ -2836,7 +2664,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>44562</v>
       </c>
       <c r="B38" t="s">
@@ -2850,7 +2678,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>44593</v>
       </c>
       <c r="B39" t="s">
@@ -2864,7 +2692,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>44621</v>
       </c>
       <c r="B40" t="s">
@@ -2878,7 +2706,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>44652</v>
       </c>
       <c r="B41" t="s">
@@ -2892,7 +2720,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>44682</v>
       </c>
       <c r="B42" t="s">
@@ -2906,7 +2734,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>44713</v>
       </c>
       <c r="B43" t="s">
@@ -2920,7 +2748,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>44743</v>
       </c>
       <c r="B44" t="s">
@@ -2934,7 +2762,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>44774</v>
       </c>
       <c r="B45" t="s">
@@ -2948,7 +2776,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>44805</v>
       </c>
       <c r="B46" t="s">
@@ -2962,7 +2790,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>44835</v>
       </c>
       <c r="B47" t="s">
@@ -2976,7 +2804,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>44866</v>
       </c>
       <c r="B48" t="s">
@@ -2990,7 +2818,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>44896</v>
       </c>
       <c r="B49" t="s">
@@ -3004,7 +2832,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>44562</v>
       </c>
       <c r="B50" t="s">
@@ -3018,7 +2846,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>44593</v>
       </c>
       <c r="B51" t="s">
@@ -3032,7 +2860,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>44621</v>
       </c>
       <c r="B52" t="s">
@@ -3046,7 +2874,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>44652</v>
       </c>
       <c r="B53" t="s">
@@ -3060,7 +2888,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
+      <c r="A54" s="1">
         <v>44682</v>
       </c>
       <c r="B54" t="s">
@@ -3074,7 +2902,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
+      <c r="A55" s="1">
         <v>44713</v>
       </c>
       <c r="B55" t="s">
@@ -3088,7 +2916,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
+      <c r="A56" s="1">
         <v>44743</v>
       </c>
       <c r="B56" t="s">
@@ -3102,7 +2930,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
+      <c r="A57" s="1">
         <v>44774</v>
       </c>
       <c r="B57" t="s">
@@ -3116,7 +2944,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
+      <c r="A58" s="1">
         <v>44805</v>
       </c>
       <c r="B58" t="s">
@@ -3130,7 +2958,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
+      <c r="A59" s="1">
         <v>44835</v>
       </c>
       <c r="B59" t="s">
@@ -3144,7 +2972,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
+      <c r="A60" s="1">
         <v>44866</v>
       </c>
       <c r="B60" t="s">
@@ -3158,7 +2986,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
+      <c r="A61" s="1">
         <v>44896</v>
       </c>
       <c r="B61" t="s">
@@ -3172,7 +3000,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
+      <c r="A62" s="1">
         <v>44562</v>
       </c>
       <c r="B62" t="s">
@@ -3186,7 +3014,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
+      <c r="A63" s="1">
         <v>44593</v>
       </c>
       <c r="B63" t="s">
@@ -3200,7 +3028,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
+      <c r="A64" s="1">
         <v>44621</v>
       </c>
       <c r="B64" t="s">
@@ -3214,7 +3042,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
+      <c r="A65" s="1">
         <v>44652</v>
       </c>
       <c r="B65" t="s">
@@ -3228,7 +3056,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
+      <c r="A66" s="1">
         <v>44682</v>
       </c>
       <c r="B66" t="s">
@@ -3242,7 +3070,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
+      <c r="A67" s="1">
         <v>44713</v>
       </c>
       <c r="B67" t="s">
@@ -3256,7 +3084,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
+      <c r="A68" s="1">
         <v>44743</v>
       </c>
       <c r="B68" t="s">
@@ -3270,7 +3098,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
+      <c r="A69" s="1">
         <v>44774</v>
       </c>
       <c r="B69" t="s">
@@ -3284,7 +3112,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
+      <c r="A70" s="1">
         <v>44805</v>
       </c>
       <c r="B70" t="s">
@@ -3298,7 +3126,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>44835</v>
       </c>
       <c r="B71" t="s">
@@ -3312,7 +3140,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
+      <c r="A72" s="1">
         <v>44866</v>
       </c>
       <c r="B72" t="s">
@@ -3326,7 +3154,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="A73" s="1">
         <v>44896</v>
       </c>
       <c r="B73" t="s">
@@ -3340,7 +3168,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="A74" s="1">
         <v>44562</v>
       </c>
       <c r="B74" t="s">
@@ -3354,7 +3182,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="A75" s="1">
         <v>44593</v>
       </c>
       <c r="B75" t="s">
@@ -3368,7 +3196,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="A76" s="1">
         <v>44621</v>
       </c>
       <c r="B76" t="s">
@@ -3382,7 +3210,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
+      <c r="A77" s="1">
         <v>44652</v>
       </c>
       <c r="B77" t="s">
@@ -3396,7 +3224,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="A78" s="1">
         <v>44682</v>
       </c>
       <c r="B78" t="s">
@@ -3410,7 +3238,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="A79" s="1">
         <v>44713</v>
       </c>
       <c r="B79" t="s">
@@ -3424,7 +3252,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
+      <c r="A80" s="1">
         <v>44743</v>
       </c>
       <c r="B80" t="s">
@@ -3438,7 +3266,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
+      <c r="A81" s="1">
         <v>44805</v>
       </c>
       <c r="B81" t="s">
@@ -3452,7 +3280,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="A82" s="1">
         <v>44835</v>
       </c>
       <c r="B82" t="s">
@@ -3466,7 +3294,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
+      <c r="A83" s="1">
         <v>44866</v>
       </c>
       <c r="B83" t="s">
@@ -3480,7 +3308,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
+      <c r="A84" s="1">
         <v>44562</v>
       </c>
       <c r="B84" t="s">
@@ -3494,7 +3322,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
+      <c r="A85" s="1">
         <v>44593</v>
       </c>
       <c r="B85" t="s">
@@ -3508,7 +3336,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
+      <c r="A86" s="1">
         <v>44621</v>
       </c>
       <c r="B86" t="s">
@@ -3522,7 +3350,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="A87" s="1">
         <v>44652</v>
       </c>
       <c r="B87" t="s">
@@ -3536,7 +3364,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
+      <c r="A88" s="1">
         <v>44682</v>
       </c>
       <c r="B88" t="s">
@@ -3550,7 +3378,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="A89" s="1">
         <v>44713</v>
       </c>
       <c r="B89" t="s">
@@ -3564,7 +3392,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
+      <c r="A90" s="1">
         <v>44743</v>
       </c>
       <c r="B90" t="s">
@@ -3578,7 +3406,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="A91" s="1">
         <v>44774</v>
       </c>
       <c r="B91" t="s">
@@ -3592,7 +3420,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
+      <c r="A92" s="1">
         <v>44805</v>
       </c>
       <c r="B92" t="s">
@@ -3606,7 +3434,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
+      <c r="A93" s="1">
         <v>44835</v>
       </c>
       <c r="B93" t="s">
@@ -3620,7 +3448,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
+      <c r="A94" s="1">
         <v>44866</v>
       </c>
       <c r="B94" t="s">
@@ -3634,7 +3462,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
+      <c r="A95" s="1">
         <v>44896</v>
       </c>
       <c r="B95" t="s">
@@ -3648,7 +3476,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
+      <c r="A96" s="1">
         <v>44562</v>
       </c>
       <c r="B96" t="s">
@@ -3662,7 +3490,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
+      <c r="A97" s="1">
         <v>44593</v>
       </c>
       <c r="B97" t="s">
@@ -3676,7 +3504,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
+      <c r="A98" s="1">
         <v>44621</v>
       </c>
       <c r="B98" t="s">
@@ -3690,7 +3518,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
+      <c r="A99" s="1">
         <v>44652</v>
       </c>
       <c r="B99" t="s">
@@ -3704,7 +3532,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
+      <c r="A100" s="1">
         <v>44682</v>
       </c>
       <c r="B100" t="s">
@@ -3718,7 +3546,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="3">
+      <c r="A101" s="1">
         <v>44713</v>
       </c>
       <c r="B101" t="s">
@@ -3732,7 +3560,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="3">
+      <c r="A102" s="1">
         <v>44743</v>
       </c>
       <c r="B102" t="s">
@@ -3746,7 +3574,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
+      <c r="A103" s="1">
         <v>44774</v>
       </c>
       <c r="B103" t="s">
@@ -3760,7 +3588,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="3">
+      <c r="A104" s="1">
         <v>44805</v>
       </c>
       <c r="B104" t="s">
@@ -3774,7 +3602,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="3">
+      <c r="A105" s="1">
         <v>44835</v>
       </c>
       <c r="B105" t="s">
@@ -3788,7 +3616,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
+      <c r="A106" s="1">
         <v>44866</v>
       </c>
       <c r="B106" t="s">
@@ -3802,7 +3630,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
+      <c r="A107" s="1">
         <v>44896</v>
       </c>
       <c r="B107" t="s">
@@ -3816,7 +3644,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
+      <c r="A108" s="1">
         <v>44562</v>
       </c>
       <c r="B108" t="s">
@@ -3830,7 +3658,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
+      <c r="A109" s="1">
         <v>44593</v>
       </c>
       <c r="B109" t="s">
@@ -3844,7 +3672,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
+      <c r="A110" s="1">
         <v>44621</v>
       </c>
       <c r="B110" t="s">
@@ -3858,7 +3686,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
+      <c r="A111" s="1">
         <v>44652</v>
       </c>
       <c r="B111" t="s">
@@ -3872,7 +3700,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
+      <c r="A112" s="1">
         <v>44682</v>
       </c>
       <c r="B112" t="s">
@@ -3886,7 +3714,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
+      <c r="A113" s="1">
         <v>44713</v>
       </c>
       <c r="B113" t="s">
@@ -3900,7 +3728,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
+      <c r="A114" s="1">
         <v>44743</v>
       </c>
       <c r="B114" t="s">
@@ -3914,7 +3742,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
+      <c r="A115" s="1">
         <v>44774</v>
       </c>
       <c r="B115" t="s">
@@ -3928,7 +3756,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
+      <c r="A116" s="1">
         <v>44805</v>
       </c>
       <c r="B116" t="s">
@@ -3942,7 +3770,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
+      <c r="A117" s="1">
         <v>44835</v>
       </c>
       <c r="B117" t="s">
@@ -3956,7 +3784,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
+      <c r="A118" s="1">
         <v>44866</v>
       </c>
       <c r="B118" t="s">
@@ -3970,7 +3798,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
+      <c r="A119" s="1">
         <v>44896</v>
       </c>
       <c r="B119" t="s">
@@ -3984,11 +3812,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -3997,25 +3822,25 @@
   <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>44927</v>
       </c>
       <c r="B2" t="s">
@@ -4029,7 +3854,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>44927</v>
       </c>
       <c r="B3" t="s">
@@ -4043,7 +3868,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>44927</v>
       </c>
       <c r="B4" t="s">
@@ -4057,7 +3882,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>44927</v>
       </c>
       <c r="B5" t="s">
@@ -4071,7 +3896,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>44927</v>
       </c>
       <c r="B6" t="s">
@@ -4085,7 +3910,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>44927</v>
       </c>
       <c r="B7" t="s">
@@ -4099,7 +3924,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>44927</v>
       </c>
       <c r="B8" t="s">
@@ -4113,7 +3938,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>44927</v>
       </c>
       <c r="B9" t="s">
@@ -4127,7 +3952,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>44958</v>
       </c>
       <c r="B10" t="s">
@@ -4141,7 +3966,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>44958</v>
       </c>
       <c r="B11" t="s">
@@ -4155,7 +3980,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>44958</v>
       </c>
       <c r="B12" t="s">
@@ -4169,7 +3994,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>44958</v>
       </c>
       <c r="B13" t="s">
@@ -4183,7 +4008,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>44958</v>
       </c>
       <c r="B14" t="s">
@@ -4197,7 +4022,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>44958</v>
       </c>
       <c r="B15" t="s">
@@ -4211,7 +4036,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>44958</v>
       </c>
       <c r="B16" t="s">
@@ -4225,7 +4050,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>44958</v>
       </c>
       <c r="B17" t="s">
@@ -4239,7 +4064,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>44986</v>
       </c>
       <c r="B18" t="s">
@@ -4253,7 +4078,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>44986</v>
       </c>
       <c r="B19" t="s">
@@ -4267,7 +4092,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>44986</v>
       </c>
       <c r="B20" t="s">
@@ -4281,7 +4106,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>44986</v>
       </c>
       <c r="B21" t="s">
@@ -4295,7 +4120,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>44986</v>
       </c>
       <c r="B22" t="s">
@@ -4309,7 +4134,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>44986</v>
       </c>
       <c r="B23" t="s">
@@ -4323,7 +4148,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>44986</v>
       </c>
       <c r="B24" t="s">
@@ -4337,7 +4162,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>44986</v>
       </c>
       <c r="B25" t="s">
@@ -4351,7 +4176,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>45017</v>
       </c>
       <c r="B26" t="s">
@@ -4365,7 +4190,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>45017</v>
       </c>
       <c r="B27" t="s">
@@ -4379,7 +4204,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>45017</v>
       </c>
       <c r="B28" t="s">
@@ -4393,7 +4218,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>45017</v>
       </c>
       <c r="B29" t="s">
@@ -4407,7 +4232,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>45017</v>
       </c>
       <c r="B30" t="s">
@@ -4421,7 +4246,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>45017</v>
       </c>
       <c r="B31" t="s">
@@ -4435,7 +4260,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>45017</v>
       </c>
       <c r="B32" t="s">
@@ -4449,7 +4274,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>45017</v>
       </c>
       <c r="B33" t="s">
@@ -4463,7 +4288,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>45047</v>
       </c>
       <c r="B34" t="s">
@@ -4477,7 +4302,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>45047</v>
       </c>
       <c r="B35" t="s">
@@ -4491,7 +4316,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>45047</v>
       </c>
       <c r="B36" t="s">
@@ -4505,7 +4330,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>45047</v>
       </c>
       <c r="B37" t="s">
@@ -4519,7 +4344,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>45047</v>
       </c>
       <c r="B38" t="s">
@@ -4533,7 +4358,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>45047</v>
       </c>
       <c r="B39" t="s">
@@ -4547,7 +4372,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>45047</v>
       </c>
       <c r="B40" t="s">
@@ -4561,7 +4386,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>45047</v>
       </c>
       <c r="B41" t="s">
@@ -4575,7 +4400,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>45078</v>
       </c>
       <c r="B42" t="s">
@@ -4589,7 +4414,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>45078</v>
       </c>
       <c r="B43" t="s">
@@ -4603,7 +4428,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>45078</v>
       </c>
       <c r="B44" t="s">
@@ -4617,7 +4442,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>45078</v>
       </c>
       <c r="B45" t="s">
@@ -4631,7 +4456,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>45078</v>
       </c>
       <c r="B46" t="s">
@@ -4645,7 +4470,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>45078</v>
       </c>
       <c r="B47" t="s">
@@ -4659,7 +4484,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>45078</v>
       </c>
       <c r="B48" t="s">
@@ -4673,7 +4498,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>45078</v>
       </c>
       <c r="B49" t="s">
@@ -4687,7 +4512,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>45108</v>
       </c>
       <c r="B50" t="s">
@@ -4701,7 +4526,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>45108</v>
       </c>
       <c r="B51" t="s">
@@ -4715,7 +4540,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>45108</v>
       </c>
       <c r="B52" t="s">
@@ -4729,7 +4554,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>45108</v>
       </c>
       <c r="B53" t="s">
@@ -4743,7 +4568,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
+      <c r="A54" s="1">
         <v>45108</v>
       </c>
       <c r="B54" t="s">
@@ -4757,7 +4582,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
+      <c r="A55" s="1">
         <v>45108</v>
       </c>
       <c r="B55" t="s">
@@ -4771,7 +4596,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
+      <c r="A56" s="1">
         <v>45108</v>
       </c>
       <c r="B56" t="s">
@@ -4785,7 +4610,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
+      <c r="A57" s="1">
         <v>45108</v>
       </c>
       <c r="B57" t="s">
@@ -4799,7 +4624,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
+      <c r="A58" s="1">
         <v>45139</v>
       </c>
       <c r="B58" t="s">
@@ -4813,7 +4638,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
+      <c r="A59" s="1">
         <v>45139</v>
       </c>
       <c r="B59" t="s">
@@ -4827,7 +4652,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
+      <c r="A60" s="1">
         <v>45139</v>
       </c>
       <c r="B60" t="s">
@@ -4841,7 +4666,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
+      <c r="A61" s="1">
         <v>45139</v>
       </c>
       <c r="B61" t="s">
@@ -4855,7 +4680,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
+      <c r="A62" s="1">
         <v>45139</v>
       </c>
       <c r="B62" t="s">
@@ -4869,7 +4694,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
+      <c r="A63" s="1">
         <v>45139</v>
       </c>
       <c r="B63" t="s">
@@ -4883,7 +4708,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
+      <c r="A64" s="1">
         <v>45139</v>
       </c>
       <c r="B64" t="s">
@@ -4897,7 +4722,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
+      <c r="A65" s="1">
         <v>45139</v>
       </c>
       <c r="B65" t="s">
@@ -4911,7 +4736,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
+      <c r="A66" s="1">
         <v>45170</v>
       </c>
       <c r="B66" t="s">
@@ -4925,7 +4750,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
+      <c r="A67" s="1">
         <v>45170</v>
       </c>
       <c r="B67" t="s">
@@ -4939,7 +4764,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
+      <c r="A68" s="1">
         <v>45170</v>
       </c>
       <c r="B68" t="s">
@@ -4953,7 +4778,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
+      <c r="A69" s="1">
         <v>45170</v>
       </c>
       <c r="B69" t="s">
@@ -4967,7 +4792,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
+      <c r="A70" s="1">
         <v>45170</v>
       </c>
       <c r="B70" t="s">
@@ -4981,7 +4806,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>45170</v>
       </c>
       <c r="B71" t="s">
@@ -4995,7 +4820,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
+      <c r="A72" s="1">
         <v>45170</v>
       </c>
       <c r="B72" t="s">
@@ -5009,7 +4834,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="A73" s="1">
         <v>45170</v>
       </c>
       <c r="B73" t="s">
@@ -5023,7 +4848,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="A74" s="1">
         <v>45200</v>
       </c>
       <c r="B74" t="s">
@@ -5037,7 +4862,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="A75" s="1">
         <v>45200</v>
       </c>
       <c r="B75" t="s">
@@ -5051,7 +4876,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="A76" s="1">
         <v>45200</v>
       </c>
       <c r="B76" t="s">
@@ -5065,7 +4890,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
+      <c r="A77" s="1">
         <v>45200</v>
       </c>
       <c r="B77" t="s">
@@ -5079,7 +4904,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="A78" s="1">
         <v>45200</v>
       </c>
       <c r="B78" t="s">
@@ -5093,7 +4918,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="A79" s="1">
         <v>45200</v>
       </c>
       <c r="B79" t="s">
@@ -5107,7 +4932,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
+      <c r="A80" s="1">
         <v>45200</v>
       </c>
       <c r="B80" t="s">
@@ -5121,7 +4946,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
+      <c r="A81" s="1">
         <v>45200</v>
       </c>
       <c r="B81" t="s">
@@ -5135,7 +4960,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="A82" s="1">
         <v>45231</v>
       </c>
       <c r="B82" t="s">
@@ -5149,7 +4974,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
+      <c r="A83" s="1">
         <v>45231</v>
       </c>
       <c r="B83" t="s">
@@ -5163,7 +4988,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
+      <c r="A84" s="1">
         <v>45231</v>
       </c>
       <c r="B84" t="s">
@@ -5177,7 +5002,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
+      <c r="A85" s="1">
         <v>45231</v>
       </c>
       <c r="B85" t="s">
@@ -5191,7 +5016,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
+      <c r="A86" s="1">
         <v>45231</v>
       </c>
       <c r="B86" t="s">
@@ -5205,7 +5030,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="A87" s="1">
         <v>45231</v>
       </c>
       <c r="B87" t="s">
@@ -5219,7 +5044,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
+      <c r="A88" s="1">
         <v>45231</v>
       </c>
       <c r="B88" t="s">
@@ -5233,7 +5058,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="A89" s="1">
         <v>45231</v>
       </c>
       <c r="B89" t="s">
@@ -5247,7 +5072,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
+      <c r="A90" s="1">
         <v>45261</v>
       </c>
       <c r="B90" t="s">
@@ -5261,7 +5086,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="A91" s="1">
         <v>45261</v>
       </c>
       <c r="B91" t="s">
@@ -5275,7 +5100,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
+      <c r="A92" s="1">
         <v>45261</v>
       </c>
       <c r="B92" t="s">
@@ -5289,7 +5114,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
+      <c r="A93" s="1">
         <v>45261</v>
       </c>
       <c r="B93" t="s">
@@ -5303,7 +5128,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
+      <c r="A94" s="1">
         <v>45261</v>
       </c>
       <c r="B94" t="s">
@@ -5317,7 +5142,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
+      <c r="A95" s="1">
         <v>45261</v>
       </c>
       <c r="B95" t="s">
@@ -5331,7 +5156,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
+      <c r="A96" s="1">
         <v>45261</v>
       </c>
       <c r="B96" t="s">
@@ -5345,7 +5170,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
+      <c r="A97" s="1">
         <v>45261</v>
       </c>
       <c r="B97" t="s">
@@ -5368,25 +5193,26 @@
   <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>45292</v>
       </c>
       <c r="B2" t="s">
@@ -5400,7 +5226,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>45292</v>
       </c>
       <c r="B3" t="s">
@@ -5414,7 +5240,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>45292</v>
       </c>
       <c r="B4" t="s">
@@ -5428,7 +5254,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>45292</v>
       </c>
       <c r="B5" t="s">
@@ -5442,7 +5268,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>45292</v>
       </c>
       <c r="B6" t="s">
@@ -5456,7 +5282,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>45292</v>
       </c>
       <c r="B7" t="s">
@@ -5470,7 +5296,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>45292</v>
       </c>
       <c r="B8" t="s">
@@ -5484,7 +5310,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>45292</v>
       </c>
       <c r="B9" t="s">
@@ -5498,7 +5324,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>45292</v>
       </c>
       <c r="B10" t="s">
@@ -5512,7 +5338,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>45292</v>
       </c>
       <c r="B11" t="s">
@@ -5526,7 +5352,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>45292</v>
       </c>
       <c r="B12" t="s">
@@ -5540,7 +5366,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>45292</v>
       </c>
       <c r="B13" t="s">
@@ -5554,7 +5380,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>45292</v>
       </c>
       <c r="B14" t="s">
@@ -5568,7 +5394,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>45292</v>
       </c>
       <c r="B15" t="s">
@@ -5582,7 +5408,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>45323</v>
       </c>
       <c r="B16" t="s">
@@ -5596,7 +5422,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>45323</v>
       </c>
       <c r="B17" t="s">
@@ -5610,7 +5436,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>45323</v>
       </c>
       <c r="B18" t="s">
@@ -5624,7 +5450,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>45323</v>
       </c>
       <c r="B19" t="s">
@@ -5638,7 +5464,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>45323</v>
       </c>
       <c r="B20" t="s">
@@ -5652,7 +5478,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>45323</v>
       </c>
       <c r="B21" t="s">
@@ -5666,7 +5492,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>45323</v>
       </c>
       <c r="B22" t="s">
@@ -5680,7 +5506,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>45323</v>
       </c>
       <c r="B23" t="s">
@@ -5694,7 +5520,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>45323</v>
       </c>
       <c r="B24" t="s">
@@ -5708,7 +5534,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>45323</v>
       </c>
       <c r="B25" t="s">
@@ -5722,7 +5548,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>45323</v>
       </c>
       <c r="B26" t="s">
@@ -5736,7 +5562,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>45323</v>
       </c>
       <c r="B27" t="s">
@@ -5750,7 +5576,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>45323</v>
       </c>
       <c r="B28" t="s">
@@ -5764,7 +5590,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>45323</v>
       </c>
       <c r="B29" t="s">
@@ -5778,7 +5604,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>45352</v>
       </c>
       <c r="B30" t="s">
@@ -5792,7 +5618,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>45352</v>
       </c>
       <c r="B31" t="s">
@@ -5806,7 +5632,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>45352</v>
       </c>
       <c r="B32" t="s">
@@ -5820,7 +5646,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>45352</v>
       </c>
       <c r="B33" t="s">
@@ -5834,7 +5660,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>45352</v>
       </c>
       <c r="B34" t="s">
@@ -5848,7 +5674,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>45352</v>
       </c>
       <c r="B35" t="s">
@@ -5862,7 +5688,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>45352</v>
       </c>
       <c r="B36" t="s">
@@ -5876,7 +5702,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>45352</v>
       </c>
       <c r="B37" t="s">
@@ -5890,7 +5716,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>45352</v>
       </c>
       <c r="B38" t="s">
@@ -5904,7 +5730,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>45352</v>
       </c>
       <c r="B39" t="s">
@@ -5918,7 +5744,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>45352</v>
       </c>
       <c r="B40" t="s">
@@ -5932,7 +5758,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>45352</v>
       </c>
       <c r="B41" t="s">
@@ -5946,7 +5772,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>45352</v>
       </c>
       <c r="B42" t="s">
@@ -5960,7 +5786,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>45352</v>
       </c>
       <c r="B43" t="s">
@@ -5974,7 +5800,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>45383</v>
       </c>
       <c r="B44" t="s">
@@ -5988,7 +5814,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>45383</v>
       </c>
       <c r="B45" t="s">
@@ -6002,7 +5828,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>45383</v>
       </c>
       <c r="B46" t="s">
@@ -6016,7 +5842,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>45383</v>
       </c>
       <c r="B47" t="s">
@@ -6030,7 +5856,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>45383</v>
       </c>
       <c r="B48" t="s">
@@ -6044,7 +5870,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>45383</v>
       </c>
       <c r="B49" t="s">
@@ -6058,7 +5884,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>45383</v>
       </c>
       <c r="B50" t="s">
@@ -6072,7 +5898,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>45383</v>
       </c>
       <c r="B51" t="s">
@@ -6086,7 +5912,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>45383</v>
       </c>
       <c r="B52" t="s">
@@ -6100,7 +5926,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>45383</v>
       </c>
       <c r="B53" t="s">
@@ -6114,7 +5940,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
+      <c r="A54" s="1">
         <v>45383</v>
       </c>
       <c r="B54" t="s">
@@ -6128,7 +5954,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
+      <c r="A55" s="1">
         <v>45383</v>
       </c>
       <c r="B55" t="s">
@@ -6142,7 +5968,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
+      <c r="A56" s="1">
         <v>45383</v>
       </c>
       <c r="B56" t="s">
@@ -6156,7 +5982,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
+      <c r="A57" s="1">
         <v>45383</v>
       </c>
       <c r="B57" t="s">
@@ -6170,7 +5996,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
+      <c r="A58" s="1">
         <v>45383</v>
       </c>
       <c r="B58" t="s">
@@ -6184,7 +6010,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
+      <c r="A59" s="1">
         <v>45413</v>
       </c>
       <c r="B59" t="s">
@@ -6198,7 +6024,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
+      <c r="A60" s="1">
         <v>45413</v>
       </c>
       <c r="B60" t="s">
@@ -6212,7 +6038,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
+      <c r="A61" s="1">
         <v>45413</v>
       </c>
       <c r="B61" t="s">
@@ -6226,7 +6052,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
+      <c r="A62" s="1">
         <v>45413</v>
       </c>
       <c r="B62" t="s">
@@ -6240,7 +6066,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
+      <c r="A63" s="1">
         <v>45413</v>
       </c>
       <c r="B63" t="s">
@@ -6254,7 +6080,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
+      <c r="A64" s="1">
         <v>45413</v>
       </c>
       <c r="B64" t="s">
@@ -6268,7 +6094,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
+      <c r="A65" s="1">
         <v>45413</v>
       </c>
       <c r="B65" t="s">
@@ -6282,7 +6108,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
+      <c r="A66" s="1">
         <v>45413</v>
       </c>
       <c r="B66" t="s">
@@ -6296,7 +6122,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
+      <c r="A67" s="1">
         <v>45413</v>
       </c>
       <c r="B67" t="s">
@@ -6310,7 +6136,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
+      <c r="A68" s="1">
         <v>45413</v>
       </c>
       <c r="B68" t="s">
@@ -6324,7 +6150,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
+      <c r="A69" s="1">
         <v>45413</v>
       </c>
       <c r="B69" t="s">
@@ -6338,7 +6164,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
+      <c r="A70" s="1">
         <v>45413</v>
       </c>
       <c r="B70" t="s">
@@ -6352,7 +6178,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>45413</v>
       </c>
       <c r="B71" t="s">
@@ -6366,7 +6192,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
+      <c r="A72" s="1">
         <v>45413</v>
       </c>
       <c r="B72" t="s">
@@ -6380,7 +6206,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="A73" s="1">
         <v>45444</v>
       </c>
       <c r="B73" t="s">
@@ -6394,7 +6220,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="A74" s="1">
         <v>45444</v>
       </c>
       <c r="B74" t="s">
@@ -6408,7 +6234,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="A75" s="1">
         <v>45444</v>
       </c>
       <c r="B75" t="s">
@@ -6422,7 +6248,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="A76" s="1">
         <v>45444</v>
       </c>
       <c r="B76" t="s">
@@ -6436,7 +6262,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
+      <c r="A77" s="1">
         <v>45444</v>
       </c>
       <c r="B77" t="s">
@@ -6450,7 +6276,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="A78" s="1">
         <v>45444</v>
       </c>
       <c r="B78" t="s">
@@ -6464,7 +6290,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="A79" s="1">
         <v>45444</v>
       </c>
       <c r="B79" t="s">
@@ -6478,7 +6304,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
+      <c r="A80" s="1">
         <v>45444</v>
       </c>
       <c r="B80" t="s">
@@ -6492,7 +6318,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
+      <c r="A81" s="1">
         <v>45444</v>
       </c>
       <c r="B81" t="s">
@@ -6506,7 +6332,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="A82" s="1">
         <v>45444</v>
       </c>
       <c r="B82" t="s">
@@ -6520,7 +6346,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
+      <c r="A83" s="1">
         <v>45444</v>
       </c>
       <c r="B83" t="s">
@@ -6534,7 +6360,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
+      <c r="A84" s="1">
         <v>45444</v>
       </c>
       <c r="B84" t="s">
@@ -6548,7 +6374,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
+      <c r="A85" s="1">
         <v>45444</v>
       </c>
       <c r="B85" t="s">
@@ -6562,7 +6388,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
+      <c r="A86" s="1">
         <v>45474</v>
       </c>
       <c r="B86" t="s">
@@ -6576,7 +6402,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="A87" s="1">
         <v>45474</v>
       </c>
       <c r="B87" t="s">
@@ -6590,7 +6416,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
+      <c r="A88" s="1">
         <v>45474</v>
       </c>
       <c r="B88" t="s">
@@ -6604,7 +6430,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="A89" s="1">
         <v>45474</v>
       </c>
       <c r="B89" t="s">
@@ -6618,7 +6444,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
+      <c r="A90" s="1">
         <v>45474</v>
       </c>
       <c r="B90" t="s">
@@ -6632,7 +6458,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="A91" s="1">
         <v>45474</v>
       </c>
       <c r="B91" t="s">
@@ -6646,7 +6472,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
+      <c r="A92" s="1">
         <v>45474</v>
       </c>
       <c r="B92" t="s">
@@ -6660,7 +6486,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
+      <c r="A93" s="1">
         <v>45474</v>
       </c>
       <c r="B93" t="s">
@@ -6674,7 +6500,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
+      <c r="A94" s="1">
         <v>45474</v>
       </c>
       <c r="B94" t="s">
@@ -6688,7 +6514,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
+      <c r="A95" s="1">
         <v>45474</v>
       </c>
       <c r="B95" t="s">
@@ -6702,7 +6528,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
+      <c r="A96" s="1">
         <v>45474</v>
       </c>
       <c r="B96" t="s">
@@ -6716,7 +6542,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
+      <c r="A97" s="1">
         <v>45474</v>
       </c>
       <c r="B97" t="s">
@@ -6730,7 +6556,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
+      <c r="A98" s="1">
         <v>45474</v>
       </c>
       <c r="B98" t="s">
@@ -6744,7 +6570,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
+      <c r="A99" s="1">
         <v>45505</v>
       </c>
       <c r="B99" t="s">
@@ -6758,7 +6584,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
+      <c r="A100" s="1">
         <v>45505</v>
       </c>
       <c r="B100" t="s">
@@ -6772,7 +6598,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="3">
+      <c r="A101" s="1">
         <v>45505</v>
       </c>
       <c r="B101" t="s">
@@ -6786,7 +6612,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="3">
+      <c r="A102" s="1">
         <v>45505</v>
       </c>
       <c r="B102" t="s">
@@ -6800,7 +6626,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
+      <c r="A103" s="1">
         <v>45505</v>
       </c>
       <c r="B103" t="s">
@@ -6814,7 +6640,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="3">
+      <c r="A104" s="1">
         <v>45505</v>
       </c>
       <c r="B104" t="s">
@@ -6828,7 +6654,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="3">
+      <c r="A105" s="1">
         <v>45505</v>
       </c>
       <c r="B105" t="s">
@@ -6842,7 +6668,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
+      <c r="A106" s="1">
         <v>45505</v>
       </c>
       <c r="B106" t="s">
@@ -6856,7 +6682,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
+      <c r="A107" s="1">
         <v>45505</v>
       </c>
       <c r="B107" t="s">
@@ -6870,7 +6696,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
+      <c r="A108" s="1">
         <v>45505</v>
       </c>
       <c r="B108" t="s">
@@ -6884,7 +6710,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
+      <c r="A109" s="1">
         <v>45505</v>
       </c>
       <c r="B109" t="s">
@@ -6898,7 +6724,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
+      <c r="A110" s="1">
         <v>45505</v>
       </c>
       <c r="B110" t="s">
@@ -6912,7 +6738,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
+      <c r="A111" s="1">
         <v>45505</v>
       </c>
       <c r="B111" t="s">
@@ -6926,7 +6752,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
+      <c r="A112" s="1">
         <v>45505</v>
       </c>
       <c r="B112" t="s">
@@ -6940,7 +6766,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
+      <c r="A113" s="1">
         <v>45536</v>
       </c>
       <c r="B113" t="s">
@@ -6954,7 +6780,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
+      <c r="A114" s="1">
         <v>45536</v>
       </c>
       <c r="B114" t="s">
@@ -6968,7 +6794,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
+      <c r="A115" s="1">
         <v>45536</v>
       </c>
       <c r="B115" t="s">
@@ -6982,7 +6808,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
+      <c r="A116" s="1">
         <v>45536</v>
       </c>
       <c r="B116" t="s">
@@ -6996,7 +6822,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
+      <c r="A117" s="1">
         <v>45536</v>
       </c>
       <c r="B117" t="s">
@@ -7010,7 +6836,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
+      <c r="A118" s="1">
         <v>45536</v>
       </c>
       <c r="B118" t="s">
@@ -7024,7 +6850,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
+      <c r="A119" s="1">
         <v>45536</v>
       </c>
       <c r="B119" t="s">
@@ -7038,7 +6864,7 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
+      <c r="A120" s="1">
         <v>45536</v>
       </c>
       <c r="B120" t="s">
@@ -7052,7 +6878,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="3">
+      <c r="A121" s="1">
         <v>45536</v>
       </c>
       <c r="B121" t="s">
@@ -7066,7 +6892,7 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="3">
+      <c r="A122" s="1">
         <v>45536</v>
       </c>
       <c r="B122" t="s">
@@ -7080,7 +6906,7 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="3">
+      <c r="A123" s="1">
         <v>45536</v>
       </c>
       <c r="B123" t="s">
@@ -7094,7 +6920,7 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="3">
+      <c r="A124" s="1">
         <v>45536</v>
       </c>
       <c r="B124" t="s">
@@ -7108,7 +6934,7 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="3">
+      <c r="A125" s="1">
         <v>45536</v>
       </c>
       <c r="B125" t="s">
@@ -7122,7 +6948,7 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="3">
+      <c r="A126" s="1">
         <v>45536</v>
       </c>
       <c r="B126" t="s">
@@ -7136,7 +6962,7 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="3">
+      <c r="A127" s="1">
         <v>45536</v>
       </c>
       <c r="B127" t="s">
@@ -7150,7 +6976,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="3">
+      <c r="A128" s="1">
         <v>45566</v>
       </c>
       <c r="B128" t="s">
@@ -7164,7 +6990,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="3">
+      <c r="A129" s="1">
         <v>45566</v>
       </c>
       <c r="B129" t="s">
@@ -7178,7 +7004,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="3">
+      <c r="A130" s="1">
         <v>45566</v>
       </c>
       <c r="B130" t="s">
@@ -7192,7 +7018,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="3">
+      <c r="A131" s="1">
         <v>45566</v>
       </c>
       <c r="B131" t="s">
@@ -7206,7 +7032,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="3">
+      <c r="A132" s="1">
         <v>45566</v>
       </c>
       <c r="B132" t="s">
@@ -7220,7 +7046,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
+      <c r="A133" s="1">
         <v>45566</v>
       </c>
       <c r="B133" t="s">
@@ -7234,7 +7060,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="3">
+      <c r="A134" s="1">
         <v>45566</v>
       </c>
       <c r="B134" t="s">
@@ -7248,7 +7074,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
+      <c r="A135" s="1">
         <v>45566</v>
       </c>
       <c r="B135" t="s">
@@ -7262,7 +7088,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="3">
+      <c r="A136" s="1">
         <v>45566</v>
       </c>
       <c r="B136" t="s">
@@ -7276,7 +7102,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="3">
+      <c r="A137" s="1">
         <v>45566</v>
       </c>
       <c r="B137" t="s">
@@ -7290,7 +7116,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
+      <c r="A138" s="1">
         <v>45566</v>
       </c>
       <c r="B138" t="s">
@@ -7304,7 +7130,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" s="3">
+      <c r="A139" s="1">
         <v>45566</v>
       </c>
       <c r="B139" t="s">
@@ -7318,7 +7144,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" s="3">
+      <c r="A140" s="1">
         <v>45566</v>
       </c>
       <c r="B140" t="s">
@@ -7332,7 +7158,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" s="3">
+      <c r="A141" s="1">
         <v>45566</v>
       </c>
       <c r="B141" t="s">
@@ -7346,7 +7172,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" s="3">
+      <c r="A142" s="1">
         <v>45597</v>
       </c>
       <c r="B142" t="s">
@@ -7360,7 +7186,7 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" s="3">
+      <c r="A143" s="1">
         <v>45597</v>
       </c>
       <c r="B143" t="s">
@@ -7374,7 +7200,7 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" s="3">
+      <c r="A144" s="1">
         <v>45597</v>
       </c>
       <c r="B144" t="s">
@@ -7388,7 +7214,7 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145" s="3">
+      <c r="A145" s="1">
         <v>45597</v>
       </c>
       <c r="B145" t="s">
@@ -7402,7 +7228,7 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146" s="3">
+      <c r="A146" s="1">
         <v>45597</v>
       </c>
       <c r="B146" t="s">
@@ -7416,7 +7242,7 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" s="3">
+      <c r="A147" s="1">
         <v>45597</v>
       </c>
       <c r="B147" t="s">
@@ -7430,7 +7256,7 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148" s="3">
+      <c r="A148" s="1">
         <v>45597</v>
       </c>
       <c r="B148" t="s">
@@ -7444,7 +7270,7 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149" s="3">
+      <c r="A149" s="1">
         <v>45597</v>
       </c>
       <c r="B149" t="s">
@@ -7458,7 +7284,7 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150" s="3">
+      <c r="A150" s="1">
         <v>45597</v>
       </c>
       <c r="B150" t="s">
@@ -7472,7 +7298,7 @@
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A151" s="3">
+      <c r="A151" s="1">
         <v>45597</v>
       </c>
       <c r="B151" t="s">
@@ -7486,7 +7312,7 @@
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A152" s="3">
+      <c r="A152" s="1">
         <v>45597</v>
       </c>
       <c r="B152" t="s">
@@ -7500,7 +7326,7 @@
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153" s="3">
+      <c r="A153" s="1">
         <v>45597</v>
       </c>
       <c r="B153" t="s">
@@ -7514,7 +7340,7 @@
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154" s="3">
+      <c r="A154" s="1">
         <v>45597</v>
       </c>
       <c r="B154" t="s">
@@ -7528,7 +7354,7 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155" s="3">
+      <c r="A155" s="1">
         <v>45597</v>
       </c>
       <c r="B155" t="s">
@@ -7542,7 +7368,7 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" s="3">
+      <c r="A156" s="1">
         <v>45597</v>
       </c>
       <c r="B156" t="s">
@@ -7556,7 +7382,7 @@
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" s="3">
+      <c r="A157" s="1">
         <v>45627</v>
       </c>
       <c r="B157" t="s">
@@ -7570,7 +7396,7 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" s="3">
+      <c r="A158" s="1">
         <v>45627</v>
       </c>
       <c r="B158" t="s">
@@ -7584,7 +7410,7 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="3">
+      <c r="A159" s="1">
         <v>45627</v>
       </c>
       <c r="B159" t="s">
@@ -7598,7 +7424,7 @@
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" s="3">
+      <c r="A160" s="1">
         <v>45627</v>
       </c>
       <c r="B160" t="s">
@@ -7612,7 +7438,7 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" s="3">
+      <c r="A161" s="1">
         <v>45627</v>
       </c>
       <c r="B161" t="s">
@@ -7626,7 +7452,7 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162" s="3">
+      <c r="A162" s="1">
         <v>45627</v>
       </c>
       <c r="B162" t="s">
@@ -7640,7 +7466,7 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163" s="3">
+      <c r="A163" s="1">
         <v>45627</v>
       </c>
       <c r="B163" t="s">
@@ -7654,7 +7480,7 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A164" s="3">
+      <c r="A164" s="1">
         <v>45627</v>
       </c>
       <c r="B164" t="s">
@@ -7668,7 +7494,7 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A165" s="3">
+      <c r="A165" s="1">
         <v>45627</v>
       </c>
       <c r="B165" t="s">
@@ -7682,7 +7508,7 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A166" s="3">
+      <c r="A166" s="1">
         <v>45627</v>
       </c>
       <c r="B166" t="s">
@@ -7696,7 +7522,7 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A167" s="3">
+      <c r="A167" s="1">
         <v>45627</v>
       </c>
       <c r="B167" t="s">
@@ -7710,7 +7536,7 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A168" s="3">
+      <c r="A168" s="1">
         <v>45627</v>
       </c>
       <c r="B168" t="s">
@@ -7724,7 +7550,7 @@
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A169" s="3">
+      <c r="A169" s="1">
         <v>45627</v>
       </c>
       <c r="B169" t="s">
@@ -7738,7 +7564,7 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A170" s="3">
+      <c r="A170" s="1">
         <v>45627</v>
       </c>
       <c r="B170" t="s">
@@ -7761,25 +7587,26 @@
   <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>45658</v>
       </c>
       <c r="B2" t="s">
@@ -7793,7 +7620,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>45658</v>
       </c>
       <c r="B3" t="s">
@@ -7807,7 +7634,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>45658</v>
       </c>
       <c r="B4" t="s">
@@ -7821,7 +7648,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>45658</v>
       </c>
       <c r="B5" t="s">
@@ -7835,7 +7662,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>45658</v>
       </c>
       <c r="B6" t="s">
@@ -7849,7 +7676,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>45689</v>
       </c>
       <c r="B7" t="s">
@@ -7863,7 +7690,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>45689</v>
       </c>
       <c r="B8" t="s">
@@ -7877,7 +7704,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>45689</v>
       </c>
       <c r="B9" t="s">
@@ -7891,7 +7718,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>45689</v>
       </c>
       <c r="B10" t="s">
@@ -7905,7 +7732,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>45689</v>
       </c>
       <c r="B11" t="s">
@@ -7919,7 +7746,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>45717</v>
       </c>
       <c r="B12" t="s">
@@ -7933,7 +7760,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>45717</v>
       </c>
       <c r="B13" t="s">
@@ -7947,7 +7774,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>45717</v>
       </c>
       <c r="B14" t="s">
@@ -7961,7 +7788,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>45717</v>
       </c>
       <c r="B15" t="s">
@@ -7975,7 +7802,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>45717</v>
       </c>
       <c r="B16" t="s">
@@ -7989,7 +7816,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>45717</v>
       </c>
       <c r="B17" t="s">
@@ -8003,7 +7830,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>45717</v>
       </c>
       <c r="B18" t="s">
@@ -8017,7 +7844,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>45717</v>
       </c>
       <c r="B19" t="s">
@@ -8031,7 +7858,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>45717</v>
       </c>
       <c r="B20" t="s">
@@ -8045,7 +7872,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>45717</v>
       </c>
       <c r="B21" t="s">
@@ -8059,7 +7886,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>45717</v>
       </c>
       <c r="B22" t="s">
@@ -8073,7 +7900,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>45717</v>
       </c>
       <c r="B23" t="s">
@@ -8087,7 +7914,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>45717</v>
       </c>
       <c r="B24" t="s">
@@ -8101,7 +7928,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>45748</v>
       </c>
       <c r="B25" t="s">
@@ -8115,7 +7942,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>45748</v>
       </c>
       <c r="B26" t="s">
@@ -8129,7 +7956,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>45748</v>
       </c>
       <c r="B27" t="s">
@@ -8143,7 +7970,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>45748</v>
       </c>
       <c r="B28" t="s">
@@ -8157,7 +7984,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>45748</v>
       </c>
       <c r="B29" t="s">
@@ -8171,7 +7998,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>45748</v>
       </c>
       <c r="B30" t="s">
@@ -8185,7 +8012,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>45748</v>
       </c>
       <c r="B31" t="s">
@@ -8199,7 +8026,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>45748</v>
       </c>
       <c r="B32" t="s">
@@ -8213,7 +8040,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>45748</v>
       </c>
       <c r="B33" t="s">
@@ -8227,7 +8054,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>45748</v>
       </c>
       <c r="B34" t="s">
@@ -8241,7 +8068,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>45748</v>
       </c>
       <c r="B35" t="s">
@@ -8255,7 +8082,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>45748</v>
       </c>
       <c r="B36" t="s">
@@ -8269,7 +8096,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>45748</v>
       </c>
       <c r="B37" t="s">
@@ -8283,7 +8110,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>45748</v>
       </c>
       <c r="B38" t="s">
@@ -8297,7 +8124,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>45778</v>
       </c>
       <c r="B39" t="s">
@@ -8311,7 +8138,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>45778</v>
       </c>
       <c r="B40" t="s">
@@ -8325,7 +8152,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>45778</v>
       </c>
       <c r="B41" t="s">
@@ -8339,7 +8166,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>45778</v>
       </c>
       <c r="B42" t="s">
@@ -8353,7 +8180,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>45778</v>
       </c>
       <c r="B43" t="s">
@@ -8367,7 +8194,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>45778</v>
       </c>
       <c r="B44" t="s">
@@ -8381,7 +8208,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>45778</v>
       </c>
       <c r="B45" t="s">
@@ -8395,7 +8222,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>45778</v>
       </c>
       <c r="B46" t="s">
@@ -8409,7 +8236,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>45778</v>
       </c>
       <c r="B47" t="s">
@@ -8423,7 +8250,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>45778</v>
       </c>
       <c r="B48" t="s">
@@ -8437,7 +8264,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>45778</v>
       </c>
       <c r="B49" t="s">
@@ -8451,7 +8278,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>45778</v>
       </c>
       <c r="B50" t="s">
@@ -8465,7 +8292,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>45778</v>
       </c>
       <c r="B51" t="s">
@@ -8479,7 +8306,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>45809</v>
       </c>
       <c r="B52" t="s">
@@ -8493,7 +8320,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>45809</v>
       </c>
       <c r="B53" t="s">
@@ -8507,7 +8334,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
+      <c r="A54" s="1">
         <v>45809</v>
       </c>
       <c r="B54" t="s">
@@ -8521,7 +8348,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
+      <c r="A55" s="1">
         <v>45809</v>
       </c>
       <c r="B55" t="s">
@@ -8535,7 +8362,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
+      <c r="A56" s="1">
         <v>45809</v>
       </c>
       <c r="B56" t="s">
@@ -8549,7 +8376,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
+      <c r="A57" s="1">
         <v>45809</v>
       </c>
       <c r="B57" t="s">
@@ -8563,7 +8390,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
+      <c r="A58" s="1">
         <v>45809</v>
       </c>
       <c r="B58" t="s">
@@ -8577,7 +8404,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
+      <c r="A59" s="1">
         <v>45809</v>
       </c>
       <c r="B59" t="s">
@@ -8591,7 +8418,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
+      <c r="A60" s="1">
         <v>45809</v>
       </c>
       <c r="B60" t="s">
@@ -8605,7 +8432,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
+      <c r="A61" s="1">
         <v>45809</v>
       </c>
       <c r="B61" t="s">
@@ -8619,7 +8446,7 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
+      <c r="A62" s="1">
         <v>45809</v>
       </c>
       <c r="B62" t="s">
@@ -8633,7 +8460,7 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
+      <c r="A63" s="1">
         <v>45809</v>
       </c>
       <c r="B63" t="s">
@@ -8647,7 +8474,7 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
+      <c r="A64" s="1">
         <v>45809</v>
       </c>
       <c r="B64" t="s">
@@ -8661,7 +8488,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
+      <c r="A65" s="1">
         <v>45809</v>
       </c>
       <c r="B65" t="s">
@@ -8675,7 +8502,7 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
+      <c r="A66" s="1">
         <v>45839</v>
       </c>
       <c r="B66" t="s">
@@ -8689,7 +8516,7 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
+      <c r="A67" s="1">
         <v>45839</v>
       </c>
       <c r="B67" t="s">
@@ -8703,7 +8530,7 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
+      <c r="A68" s="1">
         <v>45839</v>
       </c>
       <c r="B68" t="s">
@@ -8717,7 +8544,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
+      <c r="A69" s="1">
         <v>45839</v>
       </c>
       <c r="B69" t="s">
@@ -8731,7 +8558,7 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
+      <c r="A70" s="1">
         <v>45839</v>
       </c>
       <c r="B70" t="s">
@@ -8745,7 +8572,7 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>45839</v>
       </c>
       <c r="B71" t="s">
@@ -8759,7 +8586,7 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
+      <c r="A72" s="1">
         <v>45839</v>
       </c>
       <c r="B72" t="s">
@@ -8773,7 +8600,7 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
+      <c r="A73" s="1">
         <v>45839</v>
       </c>
       <c r="B73" t="s">
@@ -8787,7 +8614,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
+      <c r="A74" s="1">
         <v>45839</v>
       </c>
       <c r="B74" t="s">
@@ -8801,7 +8628,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
+      <c r="A75" s="1">
         <v>45839</v>
       </c>
       <c r="B75" t="s">
@@ -8815,7 +8642,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
+      <c r="A76" s="1">
         <v>45839</v>
       </c>
       <c r="B76" t="s">
@@ -8829,7 +8656,7 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
+      <c r="A77" s="1">
         <v>45839</v>
       </c>
       <c r="B77" t="s">
@@ -8843,7 +8670,7 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
+      <c r="A78" s="1">
         <v>45839</v>
       </c>
       <c r="B78" t="s">
@@ -8857,7 +8684,7 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
+      <c r="A79" s="1">
         <v>45839</v>
       </c>
       <c r="B79" t="s">
@@ -8871,7 +8698,7 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
+      <c r="A80" s="1">
         <v>45870</v>
       </c>
       <c r="B80" t="s">
@@ -8885,7 +8712,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
+      <c r="A81" s="1">
         <v>45870</v>
       </c>
       <c r="B81" t="s">
@@ -8899,7 +8726,7 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
+      <c r="A82" s="1">
         <v>45870</v>
       </c>
       <c r="B82" t="s">
@@ -8913,7 +8740,7 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
+      <c r="A83" s="1">
         <v>45870</v>
       </c>
       <c r="B83" t="s">
@@ -8927,7 +8754,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
+      <c r="A84" s="1">
         <v>45870</v>
       </c>
       <c r="B84" t="s">
@@ -8941,7 +8768,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
+      <c r="A85" s="1">
         <v>45870</v>
       </c>
       <c r="B85" t="s">
@@ -8955,7 +8782,7 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
+      <c r="A86" s="1">
         <v>45870</v>
       </c>
       <c r="B86" t="s">
@@ -8969,7 +8796,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
+      <c r="A87" s="1">
         <v>45870</v>
       </c>
       <c r="B87" t="s">
@@ -8983,7 +8810,7 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
+      <c r="A88" s="1">
         <v>45870</v>
       </c>
       <c r="B88" t="s">
@@ -8997,7 +8824,7 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
+      <c r="A89" s="1">
         <v>45870</v>
       </c>
       <c r="B89" t="s">
@@ -9011,7 +8838,7 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
+      <c r="A90" s="1">
         <v>45870</v>
       </c>
       <c r="B90" t="s">
@@ -9025,7 +8852,7 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
+      <c r="A91" s="1">
         <v>45870</v>
       </c>
       <c r="B91" t="s">
@@ -9039,7 +8866,7 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
+      <c r="A92" s="1">
         <v>45870</v>
       </c>
       <c r="B92" t="s">
@@ -9053,7 +8880,7 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
+      <c r="A93" s="1">
         <v>45870</v>
       </c>
       <c r="B93" t="s">
@@ -9067,7 +8894,7 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
+      <c r="A94" s="1">
         <v>45901</v>
       </c>
       <c r="B94" t="s">
@@ -9081,7 +8908,7 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
+      <c r="A95" s="1">
         <v>45901</v>
       </c>
       <c r="B95" t="s">
@@ -9095,7 +8922,7 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
+      <c r="A96" s="1">
         <v>45901</v>
       </c>
       <c r="B96" t="s">
@@ -9109,7 +8936,7 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
+      <c r="A97" s="1">
         <v>45901</v>
       </c>
       <c r="B97" t="s">
@@ -9123,7 +8950,7 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
+      <c r="A98" s="1">
         <v>45901</v>
       </c>
       <c r="B98" t="s">
@@ -9137,7 +8964,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
+      <c r="A99" s="1">
         <v>45901</v>
       </c>
       <c r="B99" t="s">
@@ -9151,7 +8978,7 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
+      <c r="A100" s="1">
         <v>45901</v>
       </c>
       <c r="B100" t="s">
@@ -9165,7 +8992,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="3">
+      <c r="A101" s="1">
         <v>45901</v>
       </c>
       <c r="B101" t="s">
@@ -9179,7 +9006,7 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="3">
+      <c r="A102" s="1">
         <v>45901</v>
       </c>
       <c r="B102" t="s">
@@ -9193,7 +9020,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
+      <c r="A103" s="1">
         <v>45901</v>
       </c>
       <c r="B103" t="s">
@@ -9207,7 +9034,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="3">
+      <c r="A104" s="1">
         <v>45901</v>
       </c>
       <c r="B104" t="s">
@@ -9221,7 +9048,7 @@
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="3">
+      <c r="A105" s="1">
         <v>45901</v>
       </c>
       <c r="B105" t="s">
@@ -9235,7 +9062,7 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
+      <c r="A106" s="1">
         <v>45901</v>
       </c>
       <c r="B106" t="s">
@@ -9249,7 +9076,7 @@
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
+      <c r="A107" s="1">
         <v>45901</v>
       </c>
       <c r="B107" t="s">
@@ -9263,7 +9090,7 @@
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
+      <c r="A108" s="1">
         <v>45901</v>
       </c>
       <c r="B108" t="s">
@@ -9277,7 +9104,7 @@
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
+      <c r="A109" s="1">
         <v>45931</v>
       </c>
       <c r="B109" t="s">
@@ -9291,7 +9118,7 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
+      <c r="A110" s="1">
         <v>45931</v>
       </c>
       <c r="B110" t="s">
@@ -9305,7 +9132,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
+      <c r="A111" s="1">
         <v>45931</v>
       </c>
       <c r="B111" t="s">
@@ -9319,7 +9146,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
+      <c r="A112" s="1">
         <v>45931</v>
       </c>
       <c r="B112" t="s">
@@ -9333,7 +9160,7 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
+      <c r="A113" s="1">
         <v>45931</v>
       </c>
       <c r="B113" t="s">
@@ -9347,7 +9174,7 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
+      <c r="A114" s="1">
         <v>45931</v>
       </c>
       <c r="B114" t="s">
@@ -9361,7 +9188,7 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
+      <c r="A115" s="1">
         <v>45931</v>
       </c>
       <c r="B115" t="s">
@@ -9375,7 +9202,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
+      <c r="A116" s="1">
         <v>45931</v>
       </c>
       <c r="B116" t="s">
@@ -9389,7 +9216,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
+      <c r="A117" s="1">
         <v>45931</v>
       </c>
       <c r="B117" t="s">
@@ -9403,7 +9230,7 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
+      <c r="A118" s="1">
         <v>45931</v>
       </c>
       <c r="B118" t="s">
@@ -9417,7 +9244,7 @@
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
+      <c r="A119" s="1">
         <v>45931</v>
       </c>
       <c r="B119" t="s">
@@ -9431,7 +9258,7 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
+      <c r="A120" s="1">
         <v>45931</v>
       </c>
       <c r="B120" t="s">
@@ -9445,7 +9272,7 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="3">
+      <c r="A121" s="1">
         <v>45931</v>
       </c>
       <c r="B121" t="s">
@@ -9459,7 +9286,7 @@
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="3">
+      <c r="A122" s="1">
         <v>45931</v>
       </c>
       <c r="B122" t="s">
@@ -9473,7 +9300,7 @@
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="3">
+      <c r="A123" s="1">
         <v>45931</v>
       </c>
       <c r="B123" t="s">
@@ -9487,7 +9314,7 @@
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="3">
+      <c r="A124" s="1">
         <v>45962</v>
       </c>
       <c r="B124" t="s">
@@ -9501,7 +9328,7 @@
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="3">
+      <c r="A125" s="1">
         <v>45962</v>
       </c>
       <c r="B125" t="s">
@@ -9515,7 +9342,7 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="3">
+      <c r="A126" s="1">
         <v>45962</v>
       </c>
       <c r="B126" t="s">
@@ -9529,7 +9356,7 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="3">
+      <c r="A127" s="1">
         <v>45962</v>
       </c>
       <c r="B127" t="s">
@@ -9543,7 +9370,7 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="3">
+      <c r="A128" s="1">
         <v>45962</v>
       </c>
       <c r="B128" t="s">
@@ -9557,7 +9384,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="3">
+      <c r="A129" s="1">
         <v>45962</v>
       </c>
       <c r="B129" t="s">
@@ -9571,7 +9398,7 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="3">
+      <c r="A130" s="1">
         <v>45962</v>
       </c>
       <c r="B130" t="s">
@@ -9585,7 +9412,7 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="3">
+      <c r="A131" s="1">
         <v>45962</v>
       </c>
       <c r="B131" t="s">
@@ -9599,7 +9426,7 @@
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="3">
+      <c r="A132" s="1">
         <v>45962</v>
       </c>
       <c r="B132" t="s">
@@ -9613,7 +9440,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
+      <c r="A133" s="1">
         <v>45962</v>
       </c>
       <c r="B133" t="s">
@@ -9627,7 +9454,7 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="3">
+      <c r="A134" s="1">
         <v>45962</v>
       </c>
       <c r="B134" t="s">
@@ -9641,7 +9468,7 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
+      <c r="A135" s="1">
         <v>45962</v>
       </c>
       <c r="B135" t="s">
@@ -9655,7 +9482,7 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="3">
+      <c r="A136" s="1">
         <v>45962</v>
       </c>
       <c r="B136" t="s">
@@ -9669,7 +9496,7 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="3">
+      <c r="A137" s="1">
         <v>45962</v>
       </c>
       <c r="B137" t="s">
@@ -9683,7 +9510,7 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
+      <c r="A138" s="1">
         <v>45962</v>
       </c>
       <c r="B138" t="s">
@@ -9697,7 +9524,7 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" s="3">
+      <c r="A139" s="1">
         <v>45992</v>
       </c>
       <c r="B139" t="s">
@@ -9711,7 +9538,7 @@
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" s="3">
+      <c r="A140" s="1">
         <v>45992</v>
       </c>
       <c r="B140" t="s">
@@ -9725,7 +9552,7 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" s="3">
+      <c r="A141" s="1">
         <v>45992</v>
       </c>
       <c r="B141" t="s">
@@ -9739,7 +9566,7 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" s="3">
+      <c r="A142" s="1">
         <v>45992</v>
       </c>
       <c r="B142" t="s">
@@ -9753,7 +9580,7 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" s="3">
+      <c r="A143" s="1">
         <v>45992</v>
       </c>
       <c r="B143" t="s">
@@ -9767,7 +9594,7 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" s="3">
+      <c r="A144" s="1">
         <v>45992</v>
       </c>
       <c r="B144" t="s">
@@ -9781,7 +9608,7 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145" s="3">
+      <c r="A145" s="1">
         <v>45992</v>
       </c>
       <c r="B145" t="s">
@@ -9795,7 +9622,7 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146" s="3">
+      <c r="A146" s="1">
         <v>45992</v>
       </c>
       <c r="B146" t="s">
@@ -9809,7 +9636,7 @@
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" s="3">
+      <c r="A147" s="1">
         <v>45992</v>
       </c>
       <c r="B147" t="s">
@@ -9823,7 +9650,7 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148" s="3">
+      <c r="A148" s="1">
         <v>45992</v>
       </c>
       <c r="B148" t="s">
@@ -9837,7 +9664,7 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149" s="3">
+      <c r="A149" s="1">
         <v>45992</v>
       </c>
       <c r="B149" t="s">
@@ -9851,7 +9678,7 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150" s="3">
+      <c r="A150" s="1">
         <v>45992</v>
       </c>
       <c r="B150" t="s">
